--- a/cell_sim/data/Mycoplasma_pneumoniae/input_data/initial_concentrations.xlsx
+++ b/cell_sim/data/Mycoplasma_pneumoniae/input_data/initial_concentrations.xlsx
@@ -7094,7 +7094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7122,6 +7122,1370 @@
         <is>
           <t>Conc (mM)</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>5-formyltetrahydrofolate</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>5fthf_e</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>C03479</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>VVIAGPKUTFNRDU-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.05002</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Acetate</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ac_e</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>C00033</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QTBSBXVTEAMEQO-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.3051</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Adenine</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ade_e</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C00147</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>GFFGJBXGBJISGV-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Adenosine</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>adn_e</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>C00212</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>OIRDTQYFTABQOQ-KQYNXXCUSA-N</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Calcium</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ca2_e</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C00076</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>BHPQYMZQTOCNFJ-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6803</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chloride</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>cl_e</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C00698</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VEXZGXHMUGYJMC-UHFFFAOYSA-M</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cholesterol</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>chsterol_e</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C00187</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>HVYWMOMLDIMFJA-DPAQBDIFSA-N</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.05026</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CoA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>coa_e</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>C00010</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RGJOEKWQDUBAIZ-IBOSZNHHSA-N</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.002928</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cytidine</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>cytd_e</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>C00475</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>UHDGCWIWMRVCDJ-XVFCMESISA-N</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>D-Glucose</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>glc__D_e</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>C00031</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>WQZGKKKJIJFFOK-GASJEMHNSA-N</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>42.78</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Deoxyadenosine</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>dad_2_e</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>C00559</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>OLXZPDWKRNYJJZ-RRKCRQDMSA-N</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.01992</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Deoxycytidine</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>dcyt_e</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>C00881</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CKTSBUTUHBMZGZ-SHYZEUOFSA-N</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.02203</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Deoxyguanosine</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>dgsn_e</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>C00330</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>YKBGVTZYEHREMT-KVQBGUIXSA-N</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.01873</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>fatty acid</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>fa_e</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>C00162</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Glycine</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>gly_e</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>C00037</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>DHMQDGOQFOQNFH-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4.333</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Guanine</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>gua_e</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>C00242</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>UYTPUPDQBNUYGX-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Guanosine</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>gsn_e</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>C00387</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NYHBQMYGNKIUIF-UUOKFMHZSA-N</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>L-Alanine</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ala__L_e</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>C00041</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>QNAYBMKLOCPYGJ-REOHCLBHSA-N</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4.14</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>L-Arginine</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>arg__L_e</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>C00062</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ODKSFYDXXFIFQN-BYPYZUCNSA-N</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4.166</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>L-Asparagine</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>asn__L_e</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>C00152</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>DCXYFEDJOCDNAF-REOHCLBHSA-N</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>L-Aspartate</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>asp__L_e</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>C00049</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CKLJMWTZIZZHCS-REOHCLBHSA-N</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.1128</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>L-Cysteine</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>cys__L_e</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>C00097</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>XUJNEKJLAYXESH-REOHCLBHSA-N</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3.168</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>L-Glutamate</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>glu__L_e</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>C00025</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>WHUUTDBJXJRKMK-VKHMYHEASA-N</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4.255</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>L-Glutamine</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>gln__L_e</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>C00064</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ZDXPYRJPNDTMRX-VKHMYHEASA-N</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>L-Histidine</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>his__L_e</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>C00135</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>HNDVDQJCIGZPNO-YFKPBYRVSA-N</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4.048</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>L-Isoleucine</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ile__L_e</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>C00407</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AGPKZVBTJJNPAG-WHFBIAKZSA-N</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4.076</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>L-Leucine</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>leu__L_e</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>C00123</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ROHFNLRQFUQHCH-YFKPBYRVSA-N</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4.229</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>L-Lysine</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>lys__L_e</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>C00047</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>KDXKERNSBIXSRK-YFKPBYRVSA-N</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4.191</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>L-Methionine</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>met__L_e</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>C00073</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>FFEARJCKVFRZRR-BYPYZUCNSA-N</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>8.050000000000001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>L-Phenylalanine</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>phe__L_e</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>C00079</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>COLNVLDHVKWLRT-QMMMGPOBSA-N</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1.076</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>L-Proline</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>pro__L_e</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>C00148</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ONIBWKKTOPOVIA-BYPYZUCNSA-N</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4.174</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>L-Serine</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ser__L_e</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>C00065</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>MTCFGRXMJLQNBG-REOHCLBHSA-N</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1.119</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>L-Threonine</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>thr__L_e</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>C00188</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AYFVYJQAPQTCCC-GBXIJSLDSA-N</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1.126</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>L-Tryptophan</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>trp__L_e</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>C00078</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>QIVBCDIJIAJPQS-VIFPVBQESA-N</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.5245</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>L-Tyrosine</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>tyr__L_e</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>C00082</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>OUYCCCASQSFEME-QMMMGPOBSA-N</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>L-Valine</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>val__L_e</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>C00183</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>KZSNJWFQEVHDMF-BYPYZUCNSA-N</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>8.106999999999999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Magnesium</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>mg2_e</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>C00305</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>JLVVSXFLKOJNIY-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1.407</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Nicotinate</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>nac_e</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>C00253</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>PVNIIMVLHYAWGP-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.0161</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Phosphate</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>pi_e</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>C00009</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NBIIXXVUZAFLBC-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Potassium</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>k_e</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>C00238</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NPYPAHLBTDXSSS-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>12.67</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>pyridoxal phosphate</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>pydx5p_e</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>C00018</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NGVDGCNFYWLIFO-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.006</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>riboflavin</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ribflv_e</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>C00255</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AUNGANRZJHBGPY-SCRDCRAPSA-N</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.003013</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Sodium</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>na1_e</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>C01330</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>FKNQFGJONOIPTF-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>19.38</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>spermine</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>sprm_e</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>C00750</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>PFNFFQXMRSDOHW-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>thiamin diphosphate</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>thmpp_e</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>C00068</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AYEKOFBPNLCAJY-UHFFFAOYSA-O</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.008015</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Thymidine</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>thymd_e</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>C00214</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>IQFYYKKMVGJFEH-XLPZGREQSA-N</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.1007</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>triacylglycerol</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>tag_e</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>C00422</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Uracil</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ura_e</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>C00106</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ISAKRJDGNUQOIC-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Uridine</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>uri_e</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>C00299</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DRTQHJPVMGBUCF-XVFCMESISA-N</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Lactate</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>lac__L_e</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Pyruvate</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>pyr_e</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Acetate</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ac_e</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Oxygen</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>o2_e</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Glycerol</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>glyc_e</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>D00028</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PEDCQBHIVMGVHV-UHFFFAOYSA-N </t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Sphingomyelin</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>sm_e</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>C00550</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WKZHECFHXLTOLJ-QYKFWSDSSA-N </t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Phosphatidylcholine</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>pc_e</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>C00157</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7135,7 +8499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7163,6 +8527,1366 @@
         <is>
           <t>Init Conc (mM)</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>atp</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>M_atp_c</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adp</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>M_adp_c</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>amp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>M_amp_c</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>gtp</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>M_gtp_c</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>gdp</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M_gdp_c</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>gmp</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>M_gmp_c</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ctp</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>M_ctp_c</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cdp</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M_cdp_c</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cmp</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>M_cmp_c</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>utp</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>M_utp_c</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>udp</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>M_udp_c</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ump</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>M_ump_c</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>datp</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>M_datp_c</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>dgtp</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>M_dgtp_c</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>dctp</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>M_dctp_c</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>dttp</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>M_dttp_c</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>nad</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>M_nad_c</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>nadh</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>M_nadh_c</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>0.083</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>nadp</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>M_nadp_c</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>0.0021</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>nadph</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>M_nadph_c</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>coa</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>M_coa_c</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>accoa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>M_accoa_c</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>fad</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>M_fad_c</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>g6p</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>M_g6p_c</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>f6p</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>M_f6p_c</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>fdp</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>M_fdp_c</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>dhap</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>M_dhap_c</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>g3p</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>M_g3p_c</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>13dpg</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>M_13dpg_c</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>0.029</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3pg</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>M_3pg_c</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2pg</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>M_2pg_c</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>pep</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>M_pep_c</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>pyr</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>M_pyr_c</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>lac--L</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>M_lac__L_c</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>cit</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>M_cit_c</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>icit</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>M_icit_c</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>akg</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>M_akg_c</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>succ</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>M_succ_c</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>fum</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>M_fum_c</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>mal--L</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>M_mal__L_c</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>oaa</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>M_oaa_c</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>0.0024</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ala--L</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>M_ala__L_c</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>arg--L</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>M_arg__L_c</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>asn--L</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>M_asn__L_c</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>asp--L</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>M_asp__L_c</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cys--L</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>M_cys__L_c</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>gln--L</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>M_gln__L_c</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>glu--L</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>M_glu__L_c</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>gly</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>M_gly_c</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>his--L</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>M_his__L_c</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="n">
+        <v>0.073</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ile--L</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>M_ile__L_c</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>leu--L</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>M_leu__L_c</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>lys--L</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>M_lys__L_c</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>met--L</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>M_met__L_c</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>phe--L</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>M_phe__L_c</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>pro--L</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>M_pro__L_c</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ser--L</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>M_ser__L_c</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>thr--L</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>M_thr__L_c</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>trp--L</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>M_trp__L_c</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>0.012</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>tyr--L</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>M_tyr__L_c</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="n">
+        <v>0.029</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>val--L</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>M_val__L_c</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>pi</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>M_pi_c</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ppi</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>M_ppi_c</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>M_h_c</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>h2o</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>M_h2o_c</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="n">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>r5p</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>M_r5p_c</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>xu5p--D</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>M_xu5p__D_c</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ru5p--D</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>M_ru5p__D_c</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>e4p</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>M_e4p_c</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>s7p</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>s7p_c</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>M_ade_c</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>gua</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>M_gua_c</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>thy</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>M_thy_c</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ura</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>M_ura_c</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>cyt</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>M_cyt_c</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>adn</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>M_adn_c</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>gsn</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>M_gsn_c</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>thymd</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>M_thymd_c</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>uri</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>M_uri_c</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>cytd</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>M_cytd_c</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
